--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7685,6 +7685,224 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128947131</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92786</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>A 15252, Bjärka, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>574115</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6405059</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128947119</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>A 15252, Bjärka, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>574115</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6405059</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 15252-2021 artfynd.xlsx
+++ b/artfynd/A 15252-2021 artfynd.xlsx
@@ -7690,7 +7690,7 @@
         <v>128947131</v>
       </c>
       <c r="B58" t="n">
-        <v>92823</v>
+        <v>92824</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>128947119</v>
       </c>
       <c r="B59" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
